--- a/alnas_xlsx/static/description/example/example_with_picture_insert.xlsx
+++ b/alnas_xlsx/static/description/example/example_with_picture_insert.xlsx
@@ -5,10 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="insert_img" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="insert_img_inside_loop" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="insert_img_cell" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="insert_img_cell_inside_loop" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="insert_img_cell_size" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="insert_img_cell_size_inside_loo" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="insert_img_cell_size_height" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="insert_img_cell_size_width" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="20">
   <si>
     <t xml:space="preserve">Report Sale Order {{docs.name}}</t>
   </si>
@@ -46,49 +53,40 @@
     <t xml:space="preserve">Price Subtotal</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">{% for o in docs.order_line %}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">{{o.price_subtotal}}</t>
-    </r>
+    <t xml:space="preserve">{% for o in docs.order_line %}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{o.price_subtotal}}</t>
   </si>
   <si>
     <t xml:space="preserve">{% insert_img o.product_id.image_1920 %}</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">{% endfor %} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Total = {{docs.amount_total}}</t>
-    </r>
+    <t xml:space="preserve">{% endfor %}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total = {{docs.amount_total}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% for o in docs.order_line %}{{o.price_subtotal}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% endfor %} Total = {{docs.amount_total}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% insert_img_cell o.product_id.image_1920 %}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% insert_img_cell o.product_id.image_1920, 200, 200%}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% for o in docs.order_line %} {{o.price_subtotal}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% insert_img_cell o.product_id.image_1920, height=250 %}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{% insert_img_cell o.product_id.image_1920, width=250 %}</t>
   </si>
 </sst>
 </file>
@@ -157,10 +155,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -212,9 +211,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -249,16 +252,24 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -450,148 +461,340 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" s="10" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="B10:H10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="1" width="13.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="2" width="13.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="2" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-    </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-    </row>
+      <c r="A10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -622,4 +825,1096 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="B10:H10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="51.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="9" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:O9"/>
+    <mergeCell ref="B10:H10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="22.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="8" style="2" width="13.54"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>